--- a/Investigacion/Parcial1/Deberes/Exccels/SLR Gamificacion technologies V2.0.xlsx
+++ b/Investigacion/Parcial1/Deberes/Exccels/SLR Gamificacion technologies V2.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Josue\Documents\GitHub\5to-2.0\Investigacion\Parcial1\Deberes\Exccels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\5to 2.0\Investigacion\Parcial1\Deberes\Exccels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F9A580B-0CD1-4C35-A477-5F1CB1678AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB30882-CF50-4415-950E-62A7D8A4E2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{CEB240E1-DB38-4149-B5E2-1E7748CE2B7C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{CEB240E1-DB38-4149-B5E2-1E7748CE2B7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Research string" sheetId="2" r:id="rId1"/>
@@ -139,9 +139,6 @@
     <t>CE5</t>
   </si>
   <si>
-    <t>Studies published before 2015 due to the constant updating of the area.</t>
-  </si>
-  <si>
     <t>CI6</t>
   </si>
   <si>
@@ -167,9 +164,6 @@
   </si>
   <si>
     <t>Review results</t>
-  </si>
-  <si>
-    <t>Years of studies analyzed 2015-2024</t>
   </si>
   <si>
     <t>First Activity</t>
@@ -932,6 +926,12 @@
   </si>
   <si>
     <t>¿Qué herramientas automatizadas realizan el control de calidad del código fuente y qué tipos de vulnerabilidades detectan?</t>
+  </si>
+  <si>
+    <t>Studies published before 2019 due to the constant updating of the area.</t>
+  </si>
+  <si>
+    <t>Years of studies analyzed 2019-2026</t>
   </si>
 </sst>
 </file>
@@ -1729,13 +1729,121 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1767,114 +1875,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2192,692 +2192,692 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC43B9F-BD75-425D-A9CA-F9EEBFA39FB2}">
   <dimension ref="A2:O69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" style="111"/>
-    <col min="2" max="2" width="16.77734375" style="111" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" style="111" customWidth="1"/>
-    <col min="4" max="4" width="29.5546875" style="111" customWidth="1"/>
-    <col min="5" max="5" width="21.21875" style="111" customWidth="1"/>
-    <col min="6" max="6" width="32.77734375" style="111" customWidth="1"/>
-    <col min="7" max="7" width="16" style="111" customWidth="1"/>
-    <col min="8" max="8" width="22.21875" style="111" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" style="111" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" style="111" customWidth="1"/>
-    <col min="11" max="12" width="11.44140625" style="111"/>
-    <col min="13" max="13" width="16.77734375" style="111" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="11.44140625" style="111"/>
+    <col min="1" max="1" width="11.42578125" style="98"/>
+    <col min="2" max="2" width="16.7109375" style="98" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="98" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" style="98" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" style="98" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" style="98" customWidth="1"/>
+    <col min="7" max="7" width="16" style="98" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" style="98" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" style="98" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="98" customWidth="1"/>
+    <col min="11" max="12" width="11.42578125" style="98"/>
+    <col min="13" max="13" width="16.7109375" style="98" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="11.42578125" style="98"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="111" t="s">
-        <v>248</v>
-      </c>
-      <c r="F2" s="111" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="98" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="98" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D4" s="90" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-    </row>
-    <row r="8" spans="1:9" ht="20.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="92">
-        <v>1</v>
-      </c>
-      <c r="C8" s="91" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D4" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="121"/>
+      <c r="I6" s="121"/>
+    </row>
+    <row r="8" spans="1:9" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="120">
+        <v>1</v>
+      </c>
+      <c r="C8" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="91"/>
-      <c r="E8" s="103"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="92"/>
-      <c r="C9" s="104" t="s">
+      <c r="D8" s="122"/>
+      <c r="E8" s="90"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="120"/>
+      <c r="C9" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="105" t="s">
+      <c r="D9" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="103"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="92"/>
-      <c r="C10" s="106" t="s">
+      <c r="E9" s="90"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="120"/>
+      <c r="C10" s="93" t="s">
+        <v>242</v>
+      </c>
+      <c r="D10" s="93" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" s="90"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="120"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93" t="s">
+        <v>256</v>
+      </c>
+      <c r="E11" s="90"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="120"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93" t="s">
+        <v>255</v>
+      </c>
+      <c r="E12" s="90"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="120"/>
+      <c r="C13" s="93" t="s">
+        <v>243</v>
+      </c>
+      <c r="D13" s="93" t="s">
         <v>244</v>
       </c>
-      <c r="D10" s="106" t="s">
+      <c r="E13" s="90"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="120"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="E14" s="90"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C15" s="93" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15" s="93" t="s">
         <v>259</v>
       </c>
-      <c r="E10" s="103"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="92"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="106" t="s">
-        <v>258</v>
-      </c>
-      <c r="E11" s="103"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="92"/>
-      <c r="C12" s="106"/>
-      <c r="D12" s="106" t="s">
-        <v>257</v>
-      </c>
-      <c r="E12" s="103"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="92"/>
-      <c r="C13" s="106" t="s">
-        <v>245</v>
-      </c>
-      <c r="D13" s="106" t="s">
-        <v>246</v>
-      </c>
-      <c r="E13" s="103"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="92"/>
-      <c r="C14" s="106"/>
-      <c r="D14" s="106" t="s">
-        <v>247</v>
-      </c>
-      <c r="E14" s="103"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="106" t="s">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C16" s="93"/>
+      <c r="D16" s="93" t="s">
         <v>260</v>
       </c>
-      <c r="D15" s="106" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="99"/>
+      <c r="D17" s="93" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="106"/>
-      <c r="D16" s="106" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="120">
+        <v>2</v>
+      </c>
+      <c r="C21" s="98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="120"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="120"/>
+      <c r="C23" s="98" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C17" s="112"/>
-      <c r="D17" s="106" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="92">
-        <v>2</v>
-      </c>
-      <c r="C21" s="111" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="92"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="92"/>
-      <c r="C23" s="111" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="92"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="92"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="92"/>
-      <c r="C26" s="113" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="120"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="120"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="120"/>
+      <c r="C26" s="100" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="92"/>
-    </row>
-    <row r="30" spans="1:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="92">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="120"/>
+    </row>
+    <row r="30" spans="1:4" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="120">
         <v>3</v>
       </c>
-      <c r="C30" s="111" t="s">
+      <c r="C30" s="98" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="92"/>
-    </row>
-    <row r="32" spans="1:4" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="92"/>
-      <c r="C32" s="111" t="s">
+    <row r="31" spans="1:4" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="120"/>
+    </row>
+    <row r="32" spans="1:4" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="120"/>
+      <c r="C32" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="111" t="s">
+      <c r="D32" s="98" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
-      <c r="C33" s="111" t="s">
+    <row r="33" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="120"/>
+      <c r="C33" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="114" t="s">
+      <c r="D33" s="101" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="92"/>
-      <c r="C34" s="111" t="s">
+    <row r="34" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="120"/>
+      <c r="C34" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="114" t="s">
+      <c r="D34" s="101" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="92"/>
-      <c r="C35" s="111" t="s">
+    <row r="35" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="120"/>
+      <c r="C35" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="D35" s="114" t="s">
+      <c r="D35" s="101" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="92"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="92"/>
-      <c r="D37" s="114"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="92"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="92">
+    <row r="36" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="120"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="120"/>
+      <c r="D37" s="101"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="120"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="120">
         <v>4</v>
       </c>
-      <c r="C41" s="111" t="s">
+      <c r="C41" s="98" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="92"/>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="120"/>
       <c r="C42" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="115" t="s">
+      <c r="D42" s="102" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="F42" s="115" t="s">
+      <c r="F42" s="102" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="92"/>
+    <row r="43" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="120"/>
       <c r="C43" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D43" s="107" t="s">
-        <v>249</v>
+      <c r="D43" s="94" t="s">
+        <v>247</v>
       </c>
       <c r="E43" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F43" s="107" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="92"/>
+      <c r="F43" s="94" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="120"/>
       <c r="C44" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D44" s="110" t="s">
-        <v>265</v>
+      <c r="D44" s="97" t="s">
+        <v>263</v>
       </c>
       <c r="E44" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="F44" s="107" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="92"/>
+      <c r="F44" s="94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="120"/>
       <c r="C45" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D45" s="108" t="s">
-        <v>250</v>
+      <c r="D45" s="95" t="s">
+        <v>248</v>
       </c>
       <c r="E45" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="F45" s="107" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="92"/>
+      <c r="F45" s="94" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="120"/>
       <c r="C46" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D46" s="109" t="s">
-        <v>251</v>
+      <c r="D46" s="96" t="s">
+        <v>249</v>
       </c>
       <c r="E46" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F46" s="107" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="92"/>
+      <c r="F46" s="94" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="120"/>
       <c r="C47" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D47" s="107" t="s">
-        <v>252</v>
+      <c r="D47" s="94" t="s">
+        <v>250</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F47" s="107" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="F47" s="94" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="61.5" x14ac:dyDescent="0.25">
       <c r="A48" s="72"/>
       <c r="C48" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="D48" s="110" t="s">
+      <c r="E48" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="F48" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="F48" s="107" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="61.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:15" ht="61.5" x14ac:dyDescent="0.25">
       <c r="A49" s="72"/>
       <c r="C49" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" s="94" t="s">
+        <v>264</v>
+      </c>
+      <c r="E49" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D49" s="107" t="s">
-        <v>266</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F49" s="107" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="F49" s="94" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="61.5" x14ac:dyDescent="0.25">
       <c r="A50" s="72"/>
       <c r="C50" s="16"/>
-      <c r="D50" s="107"/>
+      <c r="D50" s="94"/>
       <c r="E50" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F50" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="F50" s="107" t="s">
+    </row>
+    <row r="53" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="120">
+        <v>5</v>
+      </c>
+      <c r="C53" s="98" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="92">
-        <v>5</v>
-      </c>
-      <c r="C53" s="111" t="s">
+    <row r="54" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="120"/>
+    </row>
+    <row r="55" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="120"/>
+      <c r="D55" s="126" t="s">
+        <v>273</v>
+      </c>
+      <c r="E55" s="127"/>
+      <c r="F55" s="127"/>
+      <c r="G55" s="127"/>
+      <c r="H55" s="127"/>
+      <c r="I55" s="127"/>
+      <c r="J55" s="127"/>
+      <c r="K55" s="127"/>
+      <c r="L55" s="127"/>
+      <c r="M55" s="127"/>
+      <c r="N55" s="127"/>
+      <c r="O55" s="128"/>
+    </row>
+    <row r="56" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="120"/>
+      <c r="C56" s="123" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="92"/>
-    </row>
-    <row r="55" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="92"/>
-      <c r="D55" s="116" t="s">
+      <c r="D56" s="124"/>
+      <c r="E56" s="124"/>
+      <c r="F56" s="124"/>
+      <c r="G56" s="125"/>
+      <c r="H56" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="E55" s="117"/>
-      <c r="F55" s="117"/>
-      <c r="G55" s="117"/>
-      <c r="H55" s="117"/>
-      <c r="I55" s="117"/>
-      <c r="J55" s="117"/>
-      <c r="K55" s="117"/>
-      <c r="L55" s="117"/>
-      <c r="M55" s="117"/>
-      <c r="N55" s="117"/>
-      <c r="O55" s="118"/>
-    </row>
-    <row r="56" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="92"/>
-      <c r="C56" s="119" t="s">
+      <c r="I56" s="124"/>
+      <c r="J56" s="124"/>
+      <c r="K56" s="125"/>
+      <c r="L56" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="D56" s="120"/>
-      <c r="E56" s="120"/>
-      <c r="F56" s="120"/>
-      <c r="G56" s="121"/>
-      <c r="H56" s="119" t="s">
+      <c r="M56" s="124"/>
+      <c r="N56" s="124"/>
+      <c r="O56" s="125"/>
+    </row>
+    <row r="57" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="120"/>
+      <c r="C57" s="103" t="s">
         <v>44</v>
       </c>
-      <c r="I56" s="120"/>
-      <c r="J56" s="120"/>
-      <c r="K56" s="121"/>
-      <c r="L56" s="119" t="s">
+      <c r="D57" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="M56" s="120"/>
-      <c r="N56" s="120"/>
-      <c r="O56" s="121"/>
-    </row>
-    <row r="57" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="92"/>
-      <c r="C57" s="122" t="s">
+      <c r="E57" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="D57" s="123" t="s">
+      <c r="F57" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="E57" s="124" t="s">
+      <c r="G57" s="106" t="s">
         <v>48</v>
       </c>
-      <c r="F57" s="124" t="s">
+      <c r="H57" s="104" t="s">
+        <v>45</v>
+      </c>
+      <c r="I57" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="J57" s="105" t="s">
+        <v>47</v>
+      </c>
+      <c r="K57" s="106" t="s">
+        <v>48</v>
+      </c>
+      <c r="L57" s="104" t="s">
+        <v>45</v>
+      </c>
+      <c r="M57" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="N57" s="105" t="s">
+        <v>47</v>
+      </c>
+      <c r="O57" s="106" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="120"/>
+      <c r="C58" s="107" t="s">
         <v>49</v>
       </c>
-      <c r="G57" s="125" t="s">
+      <c r="D58" s="108">
+        <v>370</v>
+      </c>
+      <c r="E58" s="98">
+        <v>303</v>
+      </c>
+      <c r="G58" s="109"/>
+      <c r="H58" s="108">
+        <v>9</v>
+      </c>
+      <c r="I58" s="110">
+        <v>3</v>
+      </c>
+      <c r="J58" s="110">
+        <v>6</v>
+      </c>
+      <c r="K58" s="109">
+        <v>0</v>
+      </c>
+      <c r="L58" s="108">
+        <v>9</v>
+      </c>
+      <c r="M58" s="98">
+        <v>2</v>
+      </c>
+      <c r="N58" s="98">
+        <v>7</v>
+      </c>
+      <c r="O58" s="109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="120"/>
+      <c r="C59" s="107" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="108">
+        <v>413</v>
+      </c>
+      <c r="E59" s="98">
+        <v>363</v>
+      </c>
+      <c r="G59" s="109"/>
+      <c r="H59" s="108">
+        <v>170</v>
+      </c>
+      <c r="I59" s="98">
+        <v>33</v>
+      </c>
+      <c r="J59" s="98">
+        <v>134</v>
+      </c>
+      <c r="K59" s="109">
+        <v>3</v>
+      </c>
+      <c r="L59" s="108">
+        <v>170</v>
+      </c>
+      <c r="M59" s="98">
+        <v>20</v>
+      </c>
+      <c r="N59" s="98">
+        <v>150</v>
+      </c>
+      <c r="O59" s="109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="120"/>
+      <c r="C60" s="107" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" s="108">
+        <v>37</v>
+      </c>
+      <c r="E60" s="98">
+        <v>25</v>
+      </c>
+      <c r="G60" s="109"/>
+      <c r="H60" s="108">
+        <v>29</v>
+      </c>
+      <c r="I60" s="98">
+        <v>6</v>
+      </c>
+      <c r="J60" s="98">
+        <v>23</v>
+      </c>
+      <c r="K60" s="109">
+        <v>0</v>
+      </c>
+      <c r="L60" s="108">
+        <v>29</v>
+      </c>
+      <c r="M60" s="98">
+        <v>4</v>
+      </c>
+      <c r="N60" s="98">
+        <v>25</v>
+      </c>
+      <c r="O60" s="109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="120"/>
+      <c r="C61" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="H57" s="123" t="s">
-        <v>47</v>
-      </c>
-      <c r="I57" s="124" t="s">
-        <v>48</v>
-      </c>
-      <c r="J57" s="124" t="s">
-        <v>49</v>
-      </c>
-      <c r="K57" s="125" t="s">
-        <v>50</v>
-      </c>
-      <c r="L57" s="123" t="s">
-        <v>47</v>
-      </c>
-      <c r="M57" s="124" t="s">
-        <v>48</v>
-      </c>
-      <c r="N57" s="124" t="s">
-        <v>49</v>
-      </c>
-      <c r="O57" s="125" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="92"/>
-      <c r="C58" s="126" t="s">
-        <v>51</v>
-      </c>
-      <c r="D58" s="127">
-        <v>370</v>
-      </c>
-      <c r="E58" s="111">
-        <v>303</v>
-      </c>
-      <c r="G58" s="128"/>
-      <c r="H58" s="127">
-        <v>9</v>
-      </c>
-      <c r="I58" s="129">
-        <v>3</v>
-      </c>
-      <c r="J58" s="129">
-        <v>6</v>
-      </c>
-      <c r="K58" s="128">
-        <v>0</v>
-      </c>
-      <c r="L58" s="127">
-        <v>9</v>
-      </c>
-      <c r="M58" s="111">
-        <v>2</v>
-      </c>
-      <c r="N58" s="111">
-        <v>7</v>
-      </c>
-      <c r="O58" s="128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="92"/>
-      <c r="C59" s="126" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="127">
-        <v>413</v>
-      </c>
-      <c r="E59" s="111">
-        <v>363</v>
-      </c>
-      <c r="G59" s="128"/>
-      <c r="H59" s="127">
-        <v>170</v>
-      </c>
-      <c r="I59" s="111">
-        <v>33</v>
-      </c>
-      <c r="J59" s="111">
-        <v>134</v>
-      </c>
-      <c r="K59" s="128">
-        <v>3</v>
-      </c>
-      <c r="L59" s="127">
-        <v>170</v>
-      </c>
-      <c r="M59" s="111">
-        <v>20</v>
-      </c>
-      <c r="N59" s="111">
-        <v>150</v>
-      </c>
-      <c r="O59" s="128">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="92"/>
-      <c r="C60" s="126" t="s">
-        <v>74</v>
-      </c>
-      <c r="D60" s="127">
-        <v>37</v>
-      </c>
-      <c r="E60" s="111">
-        <v>25</v>
-      </c>
-      <c r="G60" s="128"/>
-      <c r="H60" s="127">
-        <v>29</v>
-      </c>
-      <c r="I60" s="111">
-        <v>6</v>
-      </c>
-      <c r="J60" s="111">
-        <v>23</v>
-      </c>
-      <c r="K60" s="128">
-        <v>0</v>
-      </c>
-      <c r="L60" s="127">
-        <v>29</v>
-      </c>
-      <c r="M60" s="111">
-        <v>4</v>
-      </c>
-      <c r="N60" s="111">
-        <v>25</v>
-      </c>
-      <c r="O60" s="128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="92"/>
-      <c r="C61" s="130" t="s">
-        <v>52</v>
-      </c>
-      <c r="D61" s="131">
+      <c r="D61" s="112">
         <f>SUM(D58:D60)</f>
         <v>820</v>
       </c>
-      <c r="E61" s="132">
+      <c r="E61" s="113">
         <f>E59+E60++E58</f>
         <v>691</v>
       </c>
-      <c r="F61" s="132">
-        <f>SUM(F58:F60)</f>
+      <c r="F61" s="113">
+        <f t="shared" ref="F61:O61" si="0">SUM(F58:F60)</f>
         <v>0</v>
       </c>
-      <c r="G61" s="133">
-        <f>SUM(G58:G60)</f>
+      <c r="G61" s="114">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H61" s="131">
-        <f>SUM(H58:H60)</f>
+      <c r="H61" s="112">
+        <f t="shared" si="0"/>
         <v>208</v>
       </c>
-      <c r="I61" s="132">
-        <f>SUM(I58:I60)</f>
+      <c r="I61" s="113">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="J61" s="132">
-        <f>SUM(J58:J60)</f>
+      <c r="J61" s="113">
+        <f t="shared" si="0"/>
         <v>163</v>
       </c>
-      <c r="K61" s="134">
-        <f>SUM(K58:K60)</f>
+      <c r="K61" s="115">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="L61" s="131">
-        <f>SUM(L58:L60)</f>
+      <c r="L61" s="112">
+        <f t="shared" si="0"/>
         <v>208</v>
       </c>
-      <c r="M61" s="135">
-        <f>SUM(M58:M60)</f>
+      <c r="M61" s="116">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="N61" s="132">
-        <f>SUM(N58:N60)</f>
+      <c r="N61" s="113">
+        <f t="shared" si="0"/>
         <v>182</v>
       </c>
-      <c r="O61" s="134">
-        <f>SUM(O58:O60)</f>
+      <c r="O61" s="115">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A64" s="92">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="120">
         <v>6</v>
       </c>
-      <c r="C64" s="111" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A65" s="92"/>
-      <c r="C65" s="113" t="s">
+      <c r="C64" s="98" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A65" s="120"/>
+      <c r="C65" s="100" t="s">
+        <v>52</v>
+      </c>
+      <c r="D65" s="117" t="s">
+        <v>266</v>
+      </c>
+      <c r="E65" s="118" t="s">
+        <v>269</v>
+      </c>
+      <c r="F65" s="119"/>
+      <c r="G65" s="119"/>
+    </row>
+    <row r="66" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A66" s="120"/>
+      <c r="C66" s="100" t="s">
         <v>54</v>
       </c>
-      <c r="D65" s="136" t="s">
+      <c r="D66" s="117" t="s">
+        <v>267</v>
+      </c>
+      <c r="E66" s="117" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A67" s="120"/>
+      <c r="C67" s="98" t="s">
+        <v>56</v>
+      </c>
+      <c r="D67" s="117" t="s">
         <v>268</v>
       </c>
-      <c r="E65" s="137" t="s">
+      <c r="E67" s="117" t="s">
         <v>271</v>
       </c>
-      <c r="F65" s="138"/>
-      <c r="G65" s="138"/>
-    </row>
-    <row r="66" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A66" s="92"/>
-      <c r="C66" s="113" t="s">
-        <v>56</v>
-      </c>
-      <c r="D66" s="136" t="s">
-        <v>269</v>
-      </c>
-      <c r="E66" s="136" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="92"/>
-      <c r="C67" s="111" t="s">
-        <v>58</v>
-      </c>
-      <c r="D67" s="136" t="s">
-        <v>270</v>
-      </c>
-      <c r="E67" s="136" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="92"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="92"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="120"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D4:I6"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="H56:K56"/>
+    <mergeCell ref="L56:O56"/>
+    <mergeCell ref="D55:O55"/>
     <mergeCell ref="A8:A14"/>
     <mergeCell ref="A21:A27"/>
     <mergeCell ref="A64:A69"/>
     <mergeCell ref="A41:A47"/>
     <mergeCell ref="A53:A61"/>
     <mergeCell ref="A30:A38"/>
-    <mergeCell ref="D4:I6"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="H56:K56"/>
-    <mergeCell ref="L56:O56"/>
-    <mergeCell ref="D55:O55"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -2893,87 +2893,87 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD0137A7-FC3E-40AC-8DC3-36BBC7BEFE20}">
   <dimension ref="A1:Q43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="42.44140625" style="22" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="42.42578125" style="22" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="16.21875" customWidth="1"/>
-    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" customWidth="1"/>
-    <col min="13" max="13" width="14.21875" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="9.5546875" customWidth="1"/>
-    <col min="17" max="17" width="13.77734375" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" customWidth="1"/>
+    <col min="17" max="17" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="D1" s="94" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D1" s="130" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="131" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="131"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="129"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="129"/>
+      <c r="Q4" s="129"/>
+    </row>
+    <row r="5" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="120">
+        <v>7</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H4" s="95" t="s">
+      <c r="D5" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="95"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="95"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="93"/>
-      <c r="O4" s="93"/>
-      <c r="P4" s="93"/>
-      <c r="Q4" s="93"/>
-    </row>
-    <row r="5" spans="1:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="92">
-        <v>7</v>
-      </c>
-      <c r="C5" s="26" t="s">
+      <c r="E5" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="F5" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="G5" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="H5" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="I5" s="50" t="s">
         <v>65</v>
-      </c>
-      <c r="H5" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" s="50" t="s">
-        <v>67</v>
       </c>
       <c r="J5" s="51" t="s">
         <v>5</v>
@@ -2990,35 +2990,35 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="30"/>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="92"/>
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="120"/>
       <c r="C6" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="G6" s="36">
         <v>2020</v>
       </c>
       <c r="H6" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I6" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J6" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K6" s="43"/>
       <c r="L6" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
@@ -3026,19 +3026,19 @@
       <c r="P6" s="31"/>
       <c r="Q6" s="31"/>
     </row>
-    <row r="7" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="92"/>
+    <row r="7" spans="1:17" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="120"/>
       <c r="C7" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G7" s="36">
         <v>2022</v>
@@ -3046,10 +3046,10 @@
       <c r="H7" s="43"/>
       <c r="I7" s="43"/>
       <c r="J7" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K7" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L7" s="43"/>
       <c r="M7" s="31"/>
@@ -3058,19 +3058,19 @@
       <c r="P7" s="31"/>
       <c r="Q7" s="31"/>
     </row>
-    <row r="8" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="92"/>
+    <row r="8" spans="1:17" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="120"/>
       <c r="C8" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G8" s="36">
         <v>2021</v>
@@ -3078,10 +3078,10 @@
       <c r="H8" s="49"/>
       <c r="I8" s="49"/>
       <c r="J8" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K8" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L8" s="43"/>
       <c r="M8" s="31"/>
@@ -3090,19 +3090,19 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="31"/>
     </row>
-    <row r="9" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="92"/>
+    <row r="9" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="120"/>
       <c r="C9" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G9" s="36">
         <v>2021</v>
@@ -3110,11 +3110,11 @@
       <c r="H9" s="49"/>
       <c r="I9" s="49"/>
       <c r="J9" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K9" s="49"/>
       <c r="L9" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M9" s="31"/>
       <c r="N9" s="21"/>
@@ -3122,29 +3122,29 @@
       <c r="P9" s="31"/>
       <c r="Q9" s="31"/>
     </row>
-    <row r="10" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="92"/>
+    <row r="10" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="120"/>
       <c r="C10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="G10">
         <v>2021</v>
       </c>
       <c r="H10" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I10" s="49"/>
       <c r="J10" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K10" s="43"/>
       <c r="L10" s="43"/>
@@ -3154,30 +3154,30 @@
       <c r="P10" s="31"/>
       <c r="Q10" s="31"/>
     </row>
-    <row r="11" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="92"/>
+    <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="120"/>
       <c r="C11" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G11" s="1">
         <v>2020</v>
       </c>
       <c r="H11" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I11" s="54"/>
       <c r="J11" s="54"/>
       <c r="K11" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L11" s="55"/>
       <c r="M11" s="31"/>
@@ -3186,32 +3186,32 @@
       <c r="P11" s="31"/>
       <c r="Q11" s="31"/>
     </row>
-    <row r="12" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G12" s="1">
         <v>2020</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I12" s="26"/>
       <c r="J12" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K12" s="32"/>
       <c r="L12" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M12" s="31"/>
       <c r="N12" s="21"/>
@@ -3219,34 +3219,34 @@
       <c r="P12" s="21"/>
       <c r="Q12" s="31"/>
     </row>
-    <row r="13" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G13" s="1">
         <v>2018</v>
       </c>
       <c r="H13" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I13" s="26"/>
       <c r="J13" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K13" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L13" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M13" s="21"/>
       <c r="N13" s="21"/>
@@ -3254,18 +3254,18 @@
       <c r="P13" s="31"/>
       <c r="Q13" s="21"/>
     </row>
-    <row r="14" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G14" s="1">
         <v>2015</v>
@@ -3274,10 +3274,10 @@
       <c r="I14" s="43"/>
       <c r="J14" s="43"/>
       <c r="K14" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L14" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M14" s="21"/>
       <c r="N14" s="21"/>
@@ -3285,28 +3285,28 @@
       <c r="P14" s="31"/>
       <c r="Q14" s="21"/>
     </row>
-    <row r="15" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="C15" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G15" s="1">
         <v>2023</v>
       </c>
       <c r="H15" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I15" s="43"/>
       <c r="J15" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K15" s="32"/>
       <c r="L15" s="43"/>
@@ -3316,34 +3316,34 @@
       <c r="P15" s="31"/>
       <c r="Q15" s="31"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G16" s="1">
         <v>2021</v>
       </c>
       <c r="H16" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I16" s="26"/>
       <c r="J16" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L16" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M16" s="31"/>
       <c r="N16" s="21"/>
@@ -3351,34 +3351,34 @@
       <c r="P16" s="31"/>
       <c r="Q16" s="21"/>
     </row>
-    <row r="17" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="G17" s="1">
         <v>2019</v>
       </c>
       <c r="H17" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I17" s="26"/>
       <c r="J17" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K17" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L17" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M17" s="31"/>
       <c r="N17" s="31"/>
@@ -3386,18 +3386,18 @@
       <c r="P17" s="21"/>
       <c r="Q17" s="21"/>
     </row>
-    <row r="18" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C18" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G18" s="1">
         <v>2023</v>
@@ -3406,7 +3406,7 @@
       <c r="I18" s="26"/>
       <c r="J18" s="26"/>
       <c r="K18" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L18" s="43"/>
       <c r="M18" s="31"/>
@@ -3415,32 +3415,32 @@
       <c r="P18" s="31"/>
       <c r="Q18" s="21"/>
     </row>
-    <row r="19" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G19" s="1">
         <v>2018</v>
       </c>
       <c r="H19" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I19" s="26"/>
       <c r="J19" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K19" s="32"/>
       <c r="L19" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M19" s="31"/>
       <c r="N19" s="21"/>
@@ -3448,31 +3448,31 @@
       <c r="P19" s="31"/>
       <c r="Q19" s="31"/>
     </row>
-    <row r="20" spans="3:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:17" ht="45" x14ac:dyDescent="0.25">
       <c r="C20" s="56" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G20" s="1">
         <v>2023</v>
       </c>
       <c r="H20" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I20" s="26"/>
       <c r="J20" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L20" s="43"/>
       <c r="M20" s="31"/>
@@ -3481,18 +3481,18 @@
       <c r="P20" s="21"/>
       <c r="Q20" s="31"/>
     </row>
-    <row r="21" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G21" s="1">
         <v>2023</v>
@@ -3500,10 +3500,10 @@
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
       <c r="J21" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K21" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L21" s="43"/>
       <c r="M21" s="21"/>
@@ -3512,34 +3512,34 @@
       <c r="P21" s="21"/>
       <c r="Q21" s="21"/>
     </row>
-    <row r="22" spans="3:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:17" ht="45" x14ac:dyDescent="0.25">
       <c r="C22" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G22" s="1">
         <v>2023</v>
       </c>
       <c r="H22" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I22" s="26"/>
       <c r="J22" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K22" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L22" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M22" s="31"/>
       <c r="N22" s="21"/>
@@ -3547,18 +3547,18 @@
       <c r="P22" s="31"/>
       <c r="Q22" s="21"/>
     </row>
-    <row r="23" spans="3:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:17" ht="45" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G23" s="1">
         <v>2023</v>
@@ -3566,13 +3566,13 @@
       <c r="H23" s="23"/>
       <c r="I23" s="26"/>
       <c r="J23" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K23" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L23" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M23" s="31"/>
       <c r="N23" s="31"/>
@@ -3580,31 +3580,31 @@
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
     </row>
-    <row r="24" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C24" s="45" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="4">
         <v>2023</v>
       </c>
       <c r="H24" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I24" s="26"/>
       <c r="J24" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K24" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L24" s="43"/>
       <c r="M24" s="31"/>
@@ -3613,18 +3613,18 @@
       <c r="P24" s="31"/>
       <c r="Q24" s="21"/>
     </row>
-    <row r="25" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:17" ht="30" x14ac:dyDescent="0.25">
       <c r="C25" s="45" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G25" s="6">
         <v>2023</v>
@@ -3632,13 +3632,13 @@
       <c r="H25" s="23"/>
       <c r="I25" s="26"/>
       <c r="J25" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K25" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L25" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M25" s="31"/>
       <c r="N25" s="31"/>
@@ -3646,32 +3646,32 @@
       <c r="P25" s="31"/>
       <c r="Q25" s="21"/>
     </row>
-    <row r="26" spans="3:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="46" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G26" s="6">
         <v>2023</v>
       </c>
       <c r="H26" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I26" s="29"/>
       <c r="J26" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K26" s="44"/>
       <c r="L26" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M26" s="31"/>
       <c r="N26" s="31"/>
@@ -3679,9 +3679,9 @@
       <c r="P26" s="31"/>
       <c r="Q26" s="21"/>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C27" s="47" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>9</v>
@@ -3692,18 +3692,18 @@
         <v>2023</v>
       </c>
       <c r="H27" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C28" s="47" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>9</v>
@@ -3714,18 +3714,18 @@
         <v>2022</v>
       </c>
       <c r="H28" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C29" s="47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>9</v>
@@ -3736,22 +3736,22 @@
         <v>2022</v>
       </c>
       <c r="H29" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I29" s="6"/>
       <c r="J29" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K29" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L29" s="43" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C30" s="47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>9</v>
@@ -3762,22 +3762,22 @@
         <v>2022</v>
       </c>
       <c r="H30" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K30" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L30" s="43" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C31" s="47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>9</v>
@@ -3790,14 +3790,14 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C32" s="47" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>9</v>
@@ -3808,18 +3808,18 @@
         <v>2022</v>
       </c>
       <c r="H32" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="47" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>9</v>
@@ -3830,16 +3830,16 @@
         <v>2022</v>
       </c>
       <c r="H33" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
       <c r="K33" s="7"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="47" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>9</v>
@@ -3850,20 +3850,20 @@
         <v>2022</v>
       </c>
       <c r="H34" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K34" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>9</v>
@@ -3874,16 +3874,16 @@
         <v>2021</v>
       </c>
       <c r="H35" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
       <c r="K35" s="7"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>9</v>
@@ -3894,22 +3894,22 @@
         <v>2021</v>
       </c>
       <c r="H36" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I36" s="43"/>
       <c r="J36" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K36" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L36" s="43" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C37" s="47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>9</v>
@@ -3920,18 +3920,18 @@
         <v>2020</v>
       </c>
       <c r="H37" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
       <c r="K37" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L37" s="6"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C38" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>9</v>
@@ -3942,18 +3942,18 @@
         <v>2018</v>
       </c>
       <c r="H38" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
       <c r="K38" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C39" s="47" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>9</v>
@@ -3969,12 +3969,12 @@
       <c r="K39" s="7"/>
       <c r="L39" s="6"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C40" s="57" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E40" s="28"/>
       <c r="F40" s="28"/>
@@ -3982,23 +3982,23 @@
         <v>2023</v>
       </c>
       <c r="H40" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="43" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C41" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E41" s="28"/>
       <c r="F41" s="28"/>
@@ -4006,25 +4006,25 @@
         <v>2020</v>
       </c>
       <c r="H41" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I41" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J41" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="43" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C42" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E42" s="28"/>
       <c r="F42" s="28"/>
@@ -4032,25 +4032,25 @@
         <v>2020</v>
       </c>
       <c r="H42" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I42" s="43"/>
       <c r="J42" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K42" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L42" s="43" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C43" s="47" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E43" s="28"/>
       <c r="F43" s="28"/>
@@ -4058,15 +4058,15 @@
         <v>2020</v>
       </c>
       <c r="H43" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I43" s="6"/>
       <c r="J43" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -4084,95 +4084,95 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15A35EC6-624E-4793-93E7-EDE9E1ADFE71}">
   <dimension ref="A2:AD46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" customWidth="1"/>
     <col min="3" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="30.21875" style="64" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" style="77" customWidth="1"/>
-    <col min="7" max="7" width="55.77734375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="53.77734375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" style="64" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="77" customWidth="1"/>
+    <col min="7" max="7" width="55.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="53.7109375" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="11.21875" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="17" width="11.21875" customWidth="1"/>
-    <col min="18" max="23" width="13.77734375" customWidth="1"/>
-    <col min="24" max="24" width="10.77734375" customWidth="1"/>
-    <col min="25" max="25" width="12.5546875" customWidth="1"/>
-    <col min="26" max="26" width="10.21875" customWidth="1"/>
-    <col min="27" max="28" width="12.44140625" customWidth="1"/>
+    <col min="13" max="17" width="11.28515625" customWidth="1"/>
+    <col min="18" max="23" width="13.7109375" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" customWidth="1"/>
+    <col min="25" max="25" width="12.5703125" customWidth="1"/>
+    <col min="26" max="26" width="10.28515625" customWidth="1"/>
+    <col min="27" max="28" width="12.42578125" customWidth="1"/>
     <col min="29" max="29" width="14" customWidth="1"/>
-    <col min="30" max="30" width="11.44140625" style="22"/>
+    <col min="30" max="30" width="11.42578125" style="22"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" s="92">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" s="120">
         <v>8</v>
       </c>
-      <c r="C2" s="90" t="s">
+      <c r="C2" s="121" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+      <c r="I2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" s="120"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" s="120"/>
+      <c r="L4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" s="120"/>
+      <c r="I5" s="138" t="s">
         <v>136</v>
       </c>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" s="92"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" s="92"/>
-      <c r="L4" t="s">
+      <c r="J5" s="138"/>
+      <c r="K5" s="138"/>
+      <c r="L5" s="138"/>
+      <c r="M5" s="138"/>
+      <c r="N5" s="138"/>
+      <c r="O5" s="138"/>
+      <c r="P5" s="138"/>
+      <c r="Q5" s="138"/>
+      <c r="R5" s="138"/>
+      <c r="S5" s="138"/>
+      <c r="T5" s="138"/>
+      <c r="U5" s="138"/>
+      <c r="V5" s="138"/>
+      <c r="W5" s="138"/>
+      <c r="X5" s="138"/>
+      <c r="Y5" s="138"/>
+      <c r="Z5" s="138"/>
+      <c r="AA5" s="138"/>
+      <c r="AB5" s="138"/>
+      <c r="AC5" s="138"/>
+    </row>
+    <row r="6" spans="1:29" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="120"/>
+      <c r="I6" s="132" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" s="92"/>
-      <c r="I5" s="102" t="s">
-        <v>138</v>
-      </c>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="102"/>
-      <c r="R5" s="102"/>
-      <c r="S5" s="102"/>
-      <c r="T5" s="102"/>
-      <c r="U5" s="102"/>
-      <c r="V5" s="102"/>
-      <c r="W5" s="102"/>
-      <c r="X5" s="102"/>
-      <c r="Y5" s="102"/>
-      <c r="Z5" s="102"/>
-      <c r="AA5" s="102"/>
-      <c r="AB5" s="102"/>
-      <c r="AC5" s="102"/>
-    </row>
-    <row r="6" spans="1:29" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="92"/>
-      <c r="I6" s="96" t="s">
-        <v>139</v>
-      </c>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="97"/>
-      <c r="M6" s="97"/>
-      <c r="N6" s="98"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
+      <c r="N6" s="134"/>
       <c r="O6" s="73"/>
       <c r="P6" s="73"/>
       <c r="Q6" s="73"/>
@@ -4182,118 +4182,118 @@
       <c r="U6" s="73"/>
       <c r="V6" s="73"/>
       <c r="W6" s="73"/>
-      <c r="X6" s="99" t="s">
+      <c r="X6" s="135" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y6" s="136"/>
+      <c r="Z6" s="136"/>
+      <c r="AA6" s="136"/>
+      <c r="AB6" s="136"/>
+      <c r="AC6" s="137"/>
+    </row>
+    <row r="7" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="120"/>
+      <c r="C7" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="Y6" s="100"/>
-      <c r="Z6" s="100"/>
-      <c r="AA6" s="100"/>
-      <c r="AB6" s="100"/>
-      <c r="AC6" s="101"/>
-    </row>
-    <row r="7" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="92"/>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="78" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="I7" s="86" t="s">
         <v>143</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="I7" s="86" t="s">
+      <c r="K7" s="87" t="s">
         <v>145</v>
       </c>
-      <c r="J7" s="86" t="s">
+      <c r="L7" s="86" t="s">
         <v>146</v>
       </c>
-      <c r="K7" s="87" t="s">
+      <c r="M7" s="88" t="s">
         <v>147</v>
       </c>
-      <c r="L7" s="86" t="s">
+      <c r="N7" s="81" t="s">
         <v>148</v>
       </c>
-      <c r="M7" s="88" t="s">
+      <c r="O7" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="N7" s="81" t="s">
+      <c r="P7" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="Q7" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="R7" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="S7" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="R7" s="6" t="s">
+      <c r="T7" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="U7" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="T7" s="6" t="s">
+      <c r="V7" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="U7" s="6" t="s">
+      <c r="W7" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="V7" s="6" t="s">
+      <c r="X7" s="60" t="s">
         <v>158</v>
       </c>
-      <c r="W7" s="34" t="s">
+      <c r="Y7" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="X7" s="60" t="s">
+      <c r="Z7" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="Y7" s="8" t="s">
+      <c r="AA7" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="Z7" s="8" t="s">
+      <c r="AB7" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="AA7" s="8" t="s">
+      <c r="AC7" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="AB7" s="8" t="s">
+    </row>
+    <row r="8" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="120"/>
+      <c r="C8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="75" t="s">
         <v>164</v>
-      </c>
-      <c r="AC7" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="92"/>
-      <c r="C8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="75" t="s">
-        <v>166</v>
       </c>
       <c r="F8" s="79">
         <v>2020</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
@@ -4325,24 +4325,24 @@
       <c r="AB8" s="37"/>
       <c r="AC8" s="37"/>
     </row>
-    <row r="9" spans="1:29" ht="216" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="240" x14ac:dyDescent="0.25">
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F9" s="79">
         <v>2022</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
@@ -4372,24 +4372,24 @@
       <c r="AB9" s="37"/>
       <c r="AC9" s="37"/>
     </row>
-    <row r="10" spans="1:29" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="75" x14ac:dyDescent="0.25">
       <c r="C10" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E10" s="66" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F10" s="79">
         <v>2021</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
@@ -4421,24 +4421,24 @@
       <c r="AB10" s="37"/>
       <c r="AC10" s="37"/>
     </row>
-    <row r="11" spans="1:29" ht="144" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" ht="150" x14ac:dyDescent="0.25">
       <c r="C11" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E11" s="66" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F11" s="79">
         <v>2021</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
@@ -4472,24 +4472,24 @@
       </c>
       <c r="AC11" s="37"/>
     </row>
-    <row r="12" spans="1:29" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="150" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E12" s="75" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F12" s="77">
         <v>2021</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
@@ -4521,24 +4521,24 @@
       <c r="AB12" s="37"/>
       <c r="AC12" s="37"/>
     </row>
-    <row r="13" spans="1:29" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E13" s="66" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F13" s="79">
         <v>2020</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
@@ -4570,24 +4570,24 @@
       <c r="AB13" s="37"/>
       <c r="AC13" s="37"/>
     </row>
-    <row r="14" spans="1:29" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="120" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E14" s="75" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F14" s="79">
         <v>2020</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
@@ -4619,24 +4619,24 @@
       <c r="AB14" s="37"/>
       <c r="AC14" s="37"/>
     </row>
-    <row r="15" spans="1:29" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F15" s="79">
         <v>2018</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
@@ -4664,24 +4664,24 @@
       <c r="AB15" s="37"/>
       <c r="AC15" s="37"/>
     </row>
-    <row r="16" spans="1:29" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E16" s="76" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F16" s="79">
         <v>2015</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
@@ -4711,24 +4711,24 @@
       <c r="AB16" s="37"/>
       <c r="AC16" s="37"/>
     </row>
-    <row r="17" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:29" ht="45" x14ac:dyDescent="0.25">
       <c r="C17" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E17" s="67" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F17" s="79">
         <v>2023</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
@@ -4758,24 +4758,24 @@
       <c r="AB17" s="37"/>
       <c r="AC17" s="37"/>
     </row>
-    <row r="18" spans="3:29" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:29" ht="90" x14ac:dyDescent="0.25">
       <c r="C18" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E18" s="85" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F18" s="79">
         <v>2021</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
@@ -4809,24 +4809,24 @@
       <c r="AB18" s="37"/>
       <c r="AC18" s="37"/>
     </row>
-    <row r="19" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:29" ht="75" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E19" s="68" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F19" s="79">
         <v>2019</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
@@ -4860,24 +4860,24 @@
       <c r="AB19" s="37"/>
       <c r="AC19" s="37"/>
     </row>
-    <row r="20" spans="3:29" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:29" ht="30" x14ac:dyDescent="0.25">
       <c r="C20" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E20" s="69" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F20" s="79">
         <v>2023</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
@@ -4911,24 +4911,24 @@
       <c r="AB20" s="37"/>
       <c r="AC20" s="37"/>
     </row>
-    <row r="21" spans="3:29" ht="66.599999999999994" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:29" ht="64.5" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E21" s="69" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F21" s="79">
         <v>2018</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
@@ -4960,24 +4960,24 @@
       <c r="AB21" s="37"/>
       <c r="AC21" s="37"/>
     </row>
-    <row r="22" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:29" ht="45" x14ac:dyDescent="0.25">
       <c r="C22" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="63" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F22" s="79">
         <v>2023</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
@@ -5015,24 +5015,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:29" ht="45" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="69" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F23" s="79">
         <v>2023</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
@@ -5064,24 +5064,24 @@
       <c r="AB23" s="37"/>
       <c r="AC23" s="37"/>
     </row>
-    <row r="24" spans="3:29" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:29" ht="39" x14ac:dyDescent="0.25">
       <c r="C24" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="69" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F24" s="79">
         <v>2023</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
@@ -5111,24 +5111,24 @@
       <c r="AB24" s="37"/>
       <c r="AC24" s="37"/>
     </row>
-    <row r="25" spans="3:29" ht="53.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:29" ht="51.75" x14ac:dyDescent="0.25">
       <c r="C25" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="63" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F25" s="79">
         <v>2023</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
@@ -5160,24 +5160,24 @@
       <c r="AB25" s="38"/>
       <c r="AC25" s="38"/>
     </row>
-    <row r="26" spans="3:29" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:29" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="45" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="63" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F26" s="80">
         <v>2023</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
@@ -5201,24 +5201,24 @@
       <c r="AB26" s="38"/>
       <c r="AC26" s="38"/>
     </row>
-    <row r="27" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:29" ht="45" x14ac:dyDescent="0.25">
       <c r="C27" s="45" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E27" s="70" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F27" s="81">
         <v>2023</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I27" s="6">
         <v>1</v>
@@ -5244,24 +5244,24 @@
       <c r="AB27" s="38"/>
       <c r="AC27" s="38"/>
     </row>
-    <row r="28" spans="3:29" ht="72" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:29" ht="75" x14ac:dyDescent="0.25">
       <c r="C28" s="46" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E28" s="71" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F28" s="81">
         <v>2023</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="6">
@@ -5287,15 +5287,15 @@
       <c r="AB28" s="38"/>
       <c r="AC28" s="38"/>
     </row>
-    <row r="29" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:29" ht="60" x14ac:dyDescent="0.25">
       <c r="C29" s="47" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D29" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E29" s="62" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F29" s="82">
         <v>2023</v>
@@ -5322,15 +5322,15 @@
       <c r="AB29" s="40"/>
       <c r="AC29" s="40"/>
     </row>
-    <row r="30" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:29" ht="45" x14ac:dyDescent="0.25">
       <c r="C30" s="47" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D30" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E30" s="74" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F30" s="82">
         <v>2022</v>
@@ -5365,15 +5365,15 @@
       <c r="AB30" s="37"/>
       <c r="AC30" s="37"/>
     </row>
-    <row r="31" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:29" ht="60" x14ac:dyDescent="0.25">
       <c r="C31" s="47" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D31" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E31" s="62" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F31" s="82">
         <v>2022</v>
@@ -5400,15 +5400,15 @@
       <c r="AB31" s="37"/>
       <c r="AC31" s="37"/>
     </row>
-    <row r="32" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:29" ht="60" x14ac:dyDescent="0.25">
       <c r="C32" s="47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D32" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E32" s="74" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F32" s="82">
         <v>2022</v>
@@ -5439,15 +5439,15 @@
       <c r="AB32" s="38"/>
       <c r="AC32" s="38"/>
     </row>
-    <row r="33" spans="3:29" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:29" ht="30" x14ac:dyDescent="0.25">
       <c r="C33" s="47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D33" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E33" s="74" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F33" s="82">
         <v>2022</v>
@@ -5478,15 +5478,15 @@
       <c r="AB33" s="37"/>
       <c r="AC33" s="37"/>
     </row>
-    <row r="34" spans="3:29" ht="72" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:29" ht="90" x14ac:dyDescent="0.25">
       <c r="C34" s="47" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D34" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="62" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F34" s="82">
         <v>2022</v>
@@ -5513,15 +5513,15 @@
       <c r="AB34" s="37"/>
       <c r="AC34" s="37"/>
     </row>
-    <row r="35" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:29" ht="60" x14ac:dyDescent="0.25">
       <c r="C35" s="47" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D35" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="62" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F35" s="82">
         <v>2022</v>
@@ -5548,15 +5548,15 @@
       <c r="AB35" s="38"/>
       <c r="AC35" s="38"/>
     </row>
-    <row r="36" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:29" ht="45" x14ac:dyDescent="0.25">
       <c r="C36" s="47" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D36" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E36" s="62" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F36" s="82">
         <v>2022</v>
@@ -5585,15 +5585,15 @@
       <c r="AB36" s="37"/>
       <c r="AC36" s="37"/>
     </row>
-    <row r="37" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:29" ht="45" x14ac:dyDescent="0.25">
       <c r="C37" s="47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D37" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E37" s="62" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F37" s="82">
         <v>2021</v>
@@ -5620,15 +5620,15 @@
       <c r="AB37" s="37"/>
       <c r="AC37" s="37"/>
     </row>
-    <row r="38" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:29" ht="60" x14ac:dyDescent="0.25">
       <c r="C38" s="47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D38" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="62" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F38" s="82">
         <v>2021</v>
@@ -5655,15 +5655,15 @@
       <c r="AB38" s="38"/>
       <c r="AC38" s="38"/>
     </row>
-    <row r="39" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:29" ht="45" x14ac:dyDescent="0.25">
       <c r="C39" s="47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D39" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E39" s="62" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F39" s="83">
         <v>2020</v>
@@ -5690,15 +5690,15 @@
       <c r="AB39" s="37"/>
       <c r="AC39" s="37"/>
     </row>
-    <row r="40" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:29" ht="45" x14ac:dyDescent="0.25">
       <c r="C40" s="47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D40" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E40" s="62" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F40" s="82">
         <v>2018</v>
@@ -5725,15 +5725,15 @@
       <c r="AB40" s="37"/>
       <c r="AC40" s="37"/>
     </row>
-    <row r="41" spans="3:29" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:29" ht="30" x14ac:dyDescent="0.25">
       <c r="C41" s="47" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D41" s="36" t="s">
         <v>9</v>
       </c>
       <c r="E41" s="62" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F41" s="82">
         <v>2018</v>
@@ -5760,15 +5760,15 @@
       <c r="AB41" s="37"/>
       <c r="AC41" s="37"/>
     </row>
-    <row r="42" spans="3:29" ht="72" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:29" ht="90" x14ac:dyDescent="0.25">
       <c r="C42" s="48" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E42" s="62" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F42" s="84">
         <v>2023</v>
@@ -5795,15 +5795,15 @@
       <c r="AB42" s="37"/>
       <c r="AC42" s="37"/>
     </row>
-    <row r="43" spans="3:29" ht="72" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:29" ht="90" x14ac:dyDescent="0.25">
       <c r="C43" s="47" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E43" s="74" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F43" s="82">
         <v>2023</v>
@@ -5838,15 +5838,15 @@
       <c r="AB43" s="37"/>
       <c r="AC43" s="37"/>
     </row>
-    <row r="44" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:29" ht="60" x14ac:dyDescent="0.25">
       <c r="C44" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E44" s="74" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F44" s="82">
         <v>2023</v>
@@ -5881,15 +5881,15 @@
       <c r="AB44" s="37"/>
       <c r="AC44" s="37"/>
     </row>
-    <row r="45" spans="3:29" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:29" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="47" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E45" s="74" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F45" s="82">
         <v>2020</v>
@@ -5924,7 +5924,7 @@
       <c r="AB45" s="37"/>
       <c r="AC45" s="37"/>
     </row>
-    <row r="46" spans="3:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:29" x14ac:dyDescent="0.25">
       <c r="I46" s="41">
         <f t="shared" ref="I46:O46" si="0">SUM(I8:I45)</f>
         <v>1</v>
@@ -6025,6 +6025,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004C29EC1F39B9DD41BCCFBE989E63A9DC" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="fc06bebdbdf277271b3b7852d6872b8a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5b06a7d3-8a06-4fd7-88da-f0ff67c71e72" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0b5e6bf1bfa9b37807c2e0c964db186d" ns3:_="">
     <xsd:import namespace="5b06a7d3-8a06-4fd7-88da-f0ff67c71e72"/>
@@ -6208,22 +6223,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B985C0-369C-4698-BEEC-350B56DD384D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7BF84BE-6AFB-4495-8F40-8DFBF1912AB9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{387A6899-0EFD-41ED-99B2-369E509E51DA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6239,21 +6256,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7BF84BE-6AFB-4495-8F40-8DFBF1912AB9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B985C0-369C-4698-BEEC-350B56DD384D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Investigacion/Parcial1/Deberes/Exccels/SLR Gamificacion technologies V2.0.xlsx
+++ b/Investigacion/Parcial1/Deberes/Exccels/SLR Gamificacion technologies V2.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\5to 2.0\Investigacion\Parcial1\Deberes\Exccels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Josue\Documents\GitHub\5to-2.0\Investigacion\Parcial1\Deberes\Exccels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB30882-CF50-4415-950E-62A7D8A4E2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C405018-45B5-4C74-9E31-9EA535C7C91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{CEB240E1-DB38-4149-B5E2-1E7748CE2B7C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{CEB240E1-DB38-4149-B5E2-1E7748CE2B7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Research string" sheetId="2" r:id="rId1"/>
@@ -1819,9 +1819,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1844,6 +1841,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2192,24 +2192,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC43B9F-BD75-425D-A9CA-F9EEBFA39FB2}">
   <dimension ref="A2:O69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="98"/>
-    <col min="2" max="2" width="16.7109375" style="98" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="98" customWidth="1"/>
-    <col min="4" max="4" width="29.5703125" style="98" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" style="98" customWidth="1"/>
-    <col min="6" max="6" width="32.7109375" style="98" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="98"/>
+    <col min="2" max="2" width="16.6640625" style="98" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="98" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" style="98" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" style="98" customWidth="1"/>
+    <col min="6" max="6" width="32.6640625" style="98" customWidth="1"/>
     <col min="7" max="7" width="16" style="98" customWidth="1"/>
-    <col min="8" max="8" width="22.28515625" style="98" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" style="98" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="98" customWidth="1"/>
-    <col min="11" max="12" width="11.42578125" style="98"/>
-    <col min="13" max="13" width="16.7109375" style="98" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="11.42578125" style="98"/>
+    <col min="8" max="8" width="22.33203125" style="98" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" style="98" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" style="98" customWidth="1"/>
+    <col min="11" max="12" width="11.44140625" style="98"/>
+    <col min="13" max="13" width="16.6640625" style="98" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="11.44140625" style="98"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="98" t="s">
         <v>246</v>
       </c>
@@ -2217,44 +2217,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D4" s="121" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="121"/>
-    </row>
-    <row r="8" spans="1:9" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="120">
-        <v>1</v>
-      </c>
-      <c r="C8" s="122" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D4" s="120" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="120"/>
+    </row>
+    <row r="8" spans="1:9" ht="20.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="128">
+        <v>1</v>
+      </c>
+      <c r="C8" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="122"/>
+      <c r="D8" s="121"/>
       <c r="E8" s="90"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="120"/>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="128"/>
       <c r="C9" s="91" t="s">
         <v>3</v>
       </c>
@@ -2263,8 +2263,8 @@
       </c>
       <c r="E9" s="90"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="120"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="128"/>
       <c r="C10" s="93" t="s">
         <v>242</v>
       </c>
@@ -2273,24 +2273,24 @@
       </c>
       <c r="E10" s="90"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="120"/>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="128"/>
       <c r="C11" s="93"/>
       <c r="D11" s="93" t="s">
         <v>256</v>
       </c>
       <c r="E11" s="90"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="120"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="128"/>
       <c r="C12" s="93"/>
       <c r="D12" s="93" t="s">
         <v>255</v>
       </c>
       <c r="E12" s="90"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="120"/>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="128"/>
       <c r="C13" s="93" t="s">
         <v>243</v>
       </c>
@@ -2299,15 +2299,15 @@
       </c>
       <c r="E13" s="90"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="120"/>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="128"/>
       <c r="C14" s="93"/>
       <c r="D14" s="93" t="s">
         <v>245</v>
       </c>
       <c r="E14" s="90"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C15" s="93" t="s">
         <v>258</v>
       </c>
@@ -2315,63 +2315,63 @@
         <v>259</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C16" s="93"/>
       <c r="D16" s="93" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C17" s="99"/>
       <c r="D17" s="93" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="120">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="128">
         <v>2</v>
       </c>
       <c r="C21" s="98" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="120"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="120"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="128"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="128"/>
       <c r="C23" s="98" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="120"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="120"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="120"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="128"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="128"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="128"/>
       <c r="C26" s="100" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="120"/>
-    </row>
-    <row r="30" spans="1:4" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="120">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="128"/>
+    </row>
+    <row r="30" spans="1:4" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="128">
         <v>3</v>
       </c>
       <c r="C30" s="98" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="120"/>
-    </row>
-    <row r="32" spans="1:4" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="120"/>
+    <row r="31" spans="1:4" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="128"/>
+    </row>
+    <row r="32" spans="1:4" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="128"/>
       <c r="C32" s="98" t="s">
         <v>11</v>
       </c>
@@ -2379,8 +2379,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="120"/>
+    <row r="33" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="128"/>
       <c r="C33" s="98" t="s">
         <v>13</v>
       </c>
@@ -2388,8 +2388,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="120"/>
+    <row r="34" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="128"/>
       <c r="C34" s="98" t="s">
         <v>15</v>
       </c>
@@ -2397,8 +2397,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="120"/>
+    <row r="35" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="128"/>
       <c r="C35" s="98" t="s">
         <v>9</v>
       </c>
@@ -2406,26 +2406,26 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="120"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="120"/>
+    <row r="36" spans="1:6" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="128"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="128"/>
       <c r="D37" s="101"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="120"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="120">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="128"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="128">
         <v>4</v>
       </c>
       <c r="C41" s="98" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="120"/>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="128"/>
       <c r="C42" s="89" t="s">
         <v>19</v>
       </c>
@@ -2439,8 +2439,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="120"/>
+    <row r="43" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="128"/>
       <c r="C43" s="15" t="s">
         <v>22</v>
       </c>
@@ -2454,8 +2454,8 @@
         <v>251</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="120"/>
+    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="128"/>
       <c r="C44" s="15" t="s">
         <v>24</v>
       </c>
@@ -2469,8 +2469,8 @@
         <v>252</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="120"/>
+    <row r="45" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="128"/>
       <c r="C45" s="15" t="s">
         <v>26</v>
       </c>
@@ -2484,8 +2484,8 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="120"/>
+    <row r="46" spans="1:6" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="128"/>
       <c r="C46" s="15" t="s">
         <v>28</v>
       </c>
@@ -2499,8 +2499,8 @@
         <v>254</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="120"/>
+    <row r="47" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="128"/>
       <c r="C47" s="17" t="s">
         <v>30</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="61.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="61.2" x14ac:dyDescent="0.3">
       <c r="A48" s="72"/>
       <c r="C48" s="16" t="s">
         <v>32</v>
@@ -2529,7 +2529,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="61.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="61.2" x14ac:dyDescent="0.3">
       <c r="A49" s="72"/>
       <c r="C49" s="16" t="s">
         <v>36</v>
@@ -2544,7 +2544,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="61.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="61.2" x14ac:dyDescent="0.3">
       <c r="A50" s="72"/>
       <c r="C50" s="16"/>
       <c r="D50" s="94"/>
@@ -2555,58 +2555,58 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="120">
+    <row r="53" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="128">
         <v>5</v>
       </c>
       <c r="C53" s="98" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="120"/>
-    </row>
-    <row r="55" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="120"/>
-      <c r="D55" s="126" t="s">
+    <row r="54" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="128"/>
+    </row>
+    <row r="55" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="128"/>
+      <c r="D55" s="125" t="s">
         <v>273</v>
       </c>
-      <c r="E55" s="127"/>
-      <c r="F55" s="127"/>
-      <c r="G55" s="127"/>
-      <c r="H55" s="127"/>
-      <c r="I55" s="127"/>
-      <c r="J55" s="127"/>
-      <c r="K55" s="127"/>
-      <c r="L55" s="127"/>
-      <c r="M55" s="127"/>
-      <c r="N55" s="127"/>
-      <c r="O55" s="128"/>
-    </row>
-    <row r="56" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="120"/>
-      <c r="C56" s="123" t="s">
+      <c r="E55" s="126"/>
+      <c r="F55" s="126"/>
+      <c r="G55" s="126"/>
+      <c r="H55" s="126"/>
+      <c r="I55" s="126"/>
+      <c r="J55" s="126"/>
+      <c r="K55" s="126"/>
+      <c r="L55" s="126"/>
+      <c r="M55" s="126"/>
+      <c r="N55" s="126"/>
+      <c r="O55" s="127"/>
+    </row>
+    <row r="56" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="128"/>
+      <c r="C56" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="D56" s="124"/>
-      <c r="E56" s="124"/>
-      <c r="F56" s="124"/>
-      <c r="G56" s="125"/>
-      <c r="H56" s="123" t="s">
+      <c r="D56" s="123"/>
+      <c r="E56" s="123"/>
+      <c r="F56" s="123"/>
+      <c r="G56" s="124"/>
+      <c r="H56" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="I56" s="124"/>
-      <c r="J56" s="124"/>
-      <c r="K56" s="125"/>
-      <c r="L56" s="123" t="s">
+      <c r="I56" s="123"/>
+      <c r="J56" s="123"/>
+      <c r="K56" s="124"/>
+      <c r="L56" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="M56" s="124"/>
-      <c r="N56" s="124"/>
-      <c r="O56" s="125"/>
-    </row>
-    <row r="57" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="120"/>
+      <c r="M56" s="123"/>
+      <c r="N56" s="123"/>
+      <c r="O56" s="124"/>
+    </row>
+    <row r="57" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="128"/>
       <c r="C57" s="103" t="s">
         <v>44</v>
       </c>
@@ -2647,8 +2647,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="120"/>
+    <row r="58" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="128"/>
       <c r="C58" s="107" t="s">
         <v>49</v>
       </c>
@@ -2684,8 +2684,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="120"/>
+    <row r="59" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="128"/>
       <c r="C59" s="107" t="s">
         <v>9</v>
       </c>
@@ -2721,8 +2721,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="120"/>
+    <row r="60" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="128"/>
       <c r="C60" s="107" t="s">
         <v>72</v>
       </c>
@@ -2758,8 +2758,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="120"/>
+    <row r="61" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="128"/>
       <c r="C61" s="111" t="s">
         <v>50</v>
       </c>
@@ -2812,16 +2812,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="120">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="128">
         <v>6</v>
       </c>
       <c r="C64" s="98" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A65" s="120"/>
+    <row r="65" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A65" s="128"/>
       <c r="C65" s="100" t="s">
         <v>52</v>
       </c>
@@ -2834,8 +2834,8 @@
       <c r="F65" s="119"/>
       <c r="G65" s="119"/>
     </row>
-    <row r="66" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A66" s="120"/>
+    <row r="66" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A66" s="128"/>
       <c r="C66" s="100" t="s">
         <v>54</v>
       </c>
@@ -2846,8 +2846,8 @@
         <v>270</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="A67" s="120"/>
+    <row r="67" spans="1:7" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="128"/>
       <c r="C67" s="98" t="s">
         <v>56</v>
       </c>
@@ -2858,26 +2858,26 @@
         <v>271</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="120"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="120"/>
+    <row r="68" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="128"/>
+    </row>
+    <row r="69" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A8:A14"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="A53:A61"/>
+    <mergeCell ref="A30:A38"/>
     <mergeCell ref="D4:I6"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C56:G56"/>
     <mergeCell ref="H56:K56"/>
     <mergeCell ref="L56:O56"/>
     <mergeCell ref="D55:O55"/>
-    <mergeCell ref="A8:A14"/>
-    <mergeCell ref="A21:A27"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="A53:A61"/>
-    <mergeCell ref="A30:A38"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -2893,25 +2893,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD0137A7-FC3E-40AC-8DC3-36BBC7BEFE20}">
   <dimension ref="A1:Q43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="42.42578125" style="22" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="42.44140625" style="22" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="9.5703125" customWidth="1"/>
-    <col min="17" max="17" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.5546875" customWidth="1"/>
+    <col min="17" max="17" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="D1" s="130" t="s">
         <v>57</v>
       </c>
@@ -2923,7 +2923,7 @@
       <c r="J1" s="130"/>
       <c r="K1" s="130"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="D2" s="130"/>
       <c r="E2" s="130"/>
       <c r="F2" s="130"/>
@@ -2936,7 +2936,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H4" s="131" t="s">
         <v>58</v>
       </c>
@@ -2950,8 +2950,8 @@
       <c r="P4" s="129"/>
       <c r="Q4" s="129"/>
     </row>
-    <row r="5" spans="1:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="120">
+    <row r="5" spans="1:17" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="128">
         <v>7</v>
       </c>
       <c r="C5" s="26" t="s">
@@ -2990,8 +2990,8 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="30"/>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="120"/>
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="128"/>
       <c r="C6" s="56" t="s">
         <v>66</v>
       </c>
@@ -3026,8 +3026,8 @@
       <c r="P6" s="31"/>
       <c r="Q6" s="31"/>
     </row>
-    <row r="7" spans="1:17" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="120"/>
+    <row r="7" spans="1:17" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="128"/>
       <c r="C7" s="56" t="s">
         <v>71</v>
       </c>
@@ -3058,8 +3058,8 @@
       <c r="P7" s="31"/>
       <c r="Q7" s="31"/>
     </row>
-    <row r="8" spans="1:17" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="120"/>
+    <row r="8" spans="1:17" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="128"/>
       <c r="C8" s="1" t="s">
         <v>74</v>
       </c>
@@ -3090,8 +3090,8 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="31"/>
     </row>
-    <row r="9" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="120"/>
+    <row r="9" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="128"/>
       <c r="C9" s="1" t="s">
         <v>76</v>
       </c>
@@ -3122,8 +3122,8 @@
       <c r="P9" s="31"/>
       <c r="Q9" s="31"/>
     </row>
-    <row r="10" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120"/>
+    <row r="10" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="128"/>
       <c r="C10" s="1" t="s">
         <v>78</v>
       </c>
@@ -3154,8 +3154,8 @@
       <c r="P10" s="31"/>
       <c r="Q10" s="31"/>
     </row>
-    <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="120"/>
+    <row r="11" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="128"/>
       <c r="C11" s="1" t="s">
         <v>81</v>
       </c>
@@ -3186,7 +3186,7 @@
       <c r="P11" s="31"/>
       <c r="Q11" s="31"/>
     </row>
-    <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C12" s="1" t="s">
         <v>83</v>
       </c>
@@ -3219,7 +3219,7 @@
       <c r="P12" s="21"/>
       <c r="Q12" s="31"/>
     </row>
-    <row r="13" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
         <v>85</v>
       </c>
@@ -3254,7 +3254,7 @@
       <c r="P13" s="31"/>
       <c r="Q13" s="21"/>
     </row>
-    <row r="14" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C14" s="1" t="s">
         <v>87</v>
       </c>
@@ -3285,7 +3285,7 @@
       <c r="P14" s="31"/>
       <c r="Q14" s="21"/>
     </row>
-    <row r="15" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C15" s="56" t="s">
         <v>89</v>
       </c>
@@ -3316,7 +3316,7 @@
       <c r="P15" s="31"/>
       <c r="Q15" s="31"/>
     </row>
-    <row r="16" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
         <v>92</v>
       </c>
@@ -3351,7 +3351,7 @@
       <c r="P16" s="31"/>
       <c r="Q16" s="21"/>
     </row>
-    <row r="17" spans="3:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
         <v>94</v>
       </c>
@@ -3386,7 +3386,7 @@
       <c r="P17" s="21"/>
       <c r="Q17" s="21"/>
     </row>
-    <row r="18" spans="3:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C18" s="56" t="s">
         <v>97</v>
       </c>
@@ -3415,7 +3415,7 @@
       <c r="P18" s="31"/>
       <c r="Q18" s="21"/>
     </row>
-    <row r="19" spans="3:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="s">
         <v>100</v>
       </c>
@@ -3448,7 +3448,7 @@
       <c r="P19" s="31"/>
       <c r="Q19" s="31"/>
     </row>
-    <row r="20" spans="3:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C20" s="56" t="s">
         <v>102</v>
       </c>
@@ -3481,7 +3481,7 @@
       <c r="P20" s="21"/>
       <c r="Q20" s="31"/>
     </row>
-    <row r="21" spans="3:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C21" s="1" t="s">
         <v>104</v>
       </c>
@@ -3512,7 +3512,7 @@
       <c r="P21" s="21"/>
       <c r="Q21" s="21"/>
     </row>
-    <row r="22" spans="3:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C22" s="1" t="s">
         <v>106</v>
       </c>
@@ -3547,7 +3547,7 @@
       <c r="P22" s="31"/>
       <c r="Q22" s="21"/>
     </row>
-    <row r="23" spans="3:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C23" s="1" t="s">
         <v>108</v>
       </c>
@@ -3580,7 +3580,7 @@
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
     </row>
-    <row r="24" spans="3:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C24" s="45" t="s">
         <v>110</v>
       </c>
@@ -3613,7 +3613,7 @@
       <c r="P24" s="31"/>
       <c r="Q24" s="21"/>
     </row>
-    <row r="25" spans="3:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C25" s="45" t="s">
         <v>112</v>
       </c>
@@ -3646,7 +3646,7 @@
       <c r="P25" s="31"/>
       <c r="Q25" s="21"/>
     </row>
-    <row r="26" spans="3:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="46" t="s">
         <v>114</v>
       </c>
@@ -3679,7 +3679,7 @@
       <c r="P26" s="31"/>
       <c r="Q26" s="21"/>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C27" s="47" t="s">
         <v>116</v>
       </c>
@@ -3701,7 +3701,7 @@
       <c r="K27" s="7"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C28" s="47" t="s">
         <v>117</v>
       </c>
@@ -3723,7 +3723,7 @@
       <c r="K28" s="7"/>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C29" s="47" t="s">
         <v>118</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C30" s="47" t="s">
         <v>119</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C31" s="47" t="s">
         <v>120</v>
       </c>
@@ -3795,7 +3795,7 @@
       <c r="K31" s="7"/>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C32" s="47" t="s">
         <v>121</v>
       </c>
@@ -3817,7 +3817,7 @@
       <c r="K32" s="7"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C33" s="47" t="s">
         <v>122</v>
       </c>
@@ -3837,7 +3837,7 @@
       <c r="K33" s="7"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C34" s="47" t="s">
         <v>123</v>
       </c>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C35" s="47" t="s">
         <v>124</v>
       </c>
@@ -3881,7 +3881,7 @@
       <c r="K35" s="7"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C36" s="47" t="s">
         <v>125</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C37" s="47" t="s">
         <v>126</v>
       </c>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="L37" s="6"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C38" s="47" t="s">
         <v>127</v>
       </c>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C39" s="47" t="s">
         <v>128</v>
       </c>
@@ -3969,7 +3969,7 @@
       <c r="K39" s="7"/>
       <c r="L39" s="6"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C40" s="57" t="s">
         <v>129</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C41" s="47" t="s">
         <v>131</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C42" s="47" t="s">
         <v>132</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C43" s="47" t="s">
         <v>133</v>
       </c>
@@ -4084,61 +4084,61 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15A35EC6-624E-4793-93E7-EDE9E1ADFE71}">
   <dimension ref="A2:AD46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="4.5546875" customWidth="1"/>
     <col min="3" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="30.28515625" style="64" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" style="77" customWidth="1"/>
-    <col min="7" max="7" width="55.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="53.7109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="30.33203125" style="64" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" style="77" customWidth="1"/>
+    <col min="7" max="7" width="55.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="53.6640625" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="17" width="11.28515625" customWidth="1"/>
-    <col min="18" max="23" width="13.7109375" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" customWidth="1"/>
-    <col min="25" max="25" width="12.5703125" customWidth="1"/>
-    <col min="26" max="26" width="10.28515625" customWidth="1"/>
-    <col min="27" max="28" width="12.42578125" customWidth="1"/>
+    <col min="13" max="17" width="11.33203125" customWidth="1"/>
+    <col min="18" max="23" width="13.6640625" customWidth="1"/>
+    <col min="24" max="24" width="10.6640625" customWidth="1"/>
+    <col min="25" max="25" width="12.5546875" customWidth="1"/>
+    <col min="26" max="26" width="10.33203125" customWidth="1"/>
+    <col min="27" max="28" width="12.44140625" customWidth="1"/>
     <col min="29" max="29" width="14" customWidth="1"/>
-    <col min="30" max="30" width="11.42578125" style="22"/>
+    <col min="30" max="30" width="11.44140625" style="22"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A2" s="120">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A2" s="128">
         <v>8</v>
       </c>
-      <c r="C2" s="121" t="s">
+      <c r="C2" s="120" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
       <c r="I2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="120"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="120"/>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A3" s="128"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A4" s="128"/>
       <c r="L4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="120"/>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A5" s="128"/>
       <c r="I5" s="138" t="s">
         <v>136</v>
       </c>
@@ -4163,8 +4163,8 @@
       <c r="AB5" s="138"/>
       <c r="AC5" s="138"/>
     </row>
-    <row r="6" spans="1:29" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="120"/>
+    <row r="6" spans="1:29" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="128"/>
       <c r="I6" s="132" t="s">
         <v>137</v>
       </c>
@@ -4191,8 +4191,8 @@
       <c r="AB6" s="136"/>
       <c r="AC6" s="137"/>
     </row>
-    <row r="7" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="120"/>
+    <row r="7" spans="1:29" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="128"/>
       <c r="C7" s="2" t="s">
         <v>139</v>
       </c>
@@ -4275,8 +4275,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="120"/>
+    <row r="8" spans="1:29" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="128"/>
       <c r="C8" s="2" t="s">
         <v>66</v>
       </c>
@@ -4325,7 +4325,7 @@
       <c r="AB8" s="37"/>
       <c r="AC8" s="37"/>
     </row>
-    <row r="9" spans="1:29" ht="240" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="216" x14ac:dyDescent="0.3">
       <c r="C9" s="2" t="s">
         <v>71</v>
       </c>
@@ -4372,7 +4372,7 @@
       <c r="AB9" s="37"/>
       <c r="AC9" s="37"/>
     </row>
-    <row r="10" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="72" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
         <v>74</v>
       </c>
@@ -4421,7 +4421,7 @@
       <c r="AB10" s="37"/>
       <c r="AC10" s="37"/>
     </row>
-    <row r="11" spans="1:29" ht="150" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="144" x14ac:dyDescent="0.3">
       <c r="C11" s="1" t="s">
         <v>76</v>
       </c>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="AC11" s="37"/>
     </row>
-    <row r="12" spans="1:29" ht="150" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C12" s="1" t="s">
         <v>78</v>
       </c>
@@ -4521,7 +4521,7 @@
       <c r="AB12" s="37"/>
       <c r="AC12" s="37"/>
     </row>
-    <row r="13" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
         <v>81</v>
       </c>
@@ -4570,7 +4570,7 @@
       <c r="AB13" s="37"/>
       <c r="AC13" s="37"/>
     </row>
-    <row r="14" spans="1:29" ht="120" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="115.2" x14ac:dyDescent="0.3">
       <c r="C14" s="1" t="s">
         <v>83</v>
       </c>
@@ -4619,7 +4619,7 @@
       <c r="AB14" s="37"/>
       <c r="AC14" s="37"/>
     </row>
-    <row r="15" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
         <v>85</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="AB15" s="37"/>
       <c r="AC15" s="37"/>
     </row>
-    <row r="16" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
         <v>87</v>
       </c>
@@ -4711,7 +4711,7 @@
       <c r="AB16" s="37"/>
       <c r="AC16" s="37"/>
     </row>
-    <row r="17" spans="3:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>89</v>
       </c>
@@ -4758,7 +4758,7 @@
       <c r="AB17" s="37"/>
       <c r="AC17" s="37"/>
     </row>
-    <row r="18" spans="3:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:29" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C18" s="1" t="s">
         <v>92</v>
       </c>
@@ -4809,7 +4809,7 @@
       <c r="AB18" s="37"/>
       <c r="AC18" s="37"/>
     </row>
-    <row r="19" spans="3:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="s">
         <v>94</v>
       </c>
@@ -4860,7 +4860,7 @@
       <c r="AB19" s="37"/>
       <c r="AC19" s="37"/>
     </row>
-    <row r="20" spans="3:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:29" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C20" s="2" t="s">
         <v>97</v>
       </c>
@@ -4911,7 +4911,7 @@
       <c r="AB20" s="37"/>
       <c r="AC20" s="37"/>
     </row>
-    <row r="21" spans="3:29" ht="64.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:29" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="C21" s="1" t="s">
         <v>100</v>
       </c>
@@ -4960,7 +4960,7 @@
       <c r="AB21" s="37"/>
       <c r="AC21" s="37"/>
     </row>
-    <row r="22" spans="3:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C22" s="2" t="s">
         <v>102</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C23" s="1" t="s">
         <v>104</v>
       </c>
@@ -5064,7 +5064,7 @@
       <c r="AB23" s="37"/>
       <c r="AC23" s="37"/>
     </row>
-    <row r="24" spans="3:29" ht="39" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:29" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
         <v>106</v>
       </c>
@@ -5111,7 +5111,7 @@
       <c r="AB24" s="37"/>
       <c r="AC24" s="37"/>
     </row>
-    <row r="25" spans="3:29" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:29" ht="53.4" x14ac:dyDescent="0.3">
       <c r="C25" s="1" t="s">
         <v>108</v>
       </c>
@@ -5160,7 +5160,7 @@
       <c r="AB25" s="38"/>
       <c r="AC25" s="38"/>
     </row>
-    <row r="26" spans="3:29" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:29" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="45" t="s">
         <v>110</v>
       </c>
@@ -5201,7 +5201,7 @@
       <c r="AB26" s="38"/>
       <c r="AC26" s="38"/>
     </row>
-    <row r="27" spans="3:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C27" s="45" t="s">
         <v>112</v>
       </c>
@@ -5244,7 +5244,7 @@
       <c r="AB27" s="38"/>
       <c r="AC27" s="38"/>
     </row>
-    <row r="28" spans="3:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:29" ht="72" x14ac:dyDescent="0.3">
       <c r="C28" s="46" t="s">
         <v>114</v>
       </c>
@@ -5287,7 +5287,7 @@
       <c r="AB28" s="38"/>
       <c r="AC28" s="38"/>
     </row>
-    <row r="29" spans="3:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C29" s="47" t="s">
         <v>116</v>
       </c>
@@ -5322,7 +5322,7 @@
       <c r="AB29" s="40"/>
       <c r="AC29" s="40"/>
     </row>
-    <row r="30" spans="3:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C30" s="47" t="s">
         <v>117</v>
       </c>
@@ -5365,7 +5365,7 @@
       <c r="AB30" s="37"/>
       <c r="AC30" s="37"/>
     </row>
-    <row r="31" spans="3:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C31" s="47" t="s">
         <v>118</v>
       </c>
@@ -5400,7 +5400,7 @@
       <c r="AB31" s="37"/>
       <c r="AC31" s="37"/>
     </row>
-    <row r="32" spans="3:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C32" s="47" t="s">
         <v>119</v>
       </c>
@@ -5439,7 +5439,7 @@
       <c r="AB32" s="38"/>
       <c r="AC32" s="38"/>
     </row>
-    <row r="33" spans="3:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:29" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C33" s="47" t="s">
         <v>120</v>
       </c>
@@ -5478,7 +5478,7 @@
       <c r="AB33" s="37"/>
       <c r="AC33" s="37"/>
     </row>
-    <row r="34" spans="3:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:29" ht="72" x14ac:dyDescent="0.3">
       <c r="C34" s="47" t="s">
         <v>121</v>
       </c>
@@ -5513,7 +5513,7 @@
       <c r="AB34" s="37"/>
       <c r="AC34" s="37"/>
     </row>
-    <row r="35" spans="3:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C35" s="47" t="s">
         <v>122</v>
       </c>
@@ -5548,7 +5548,7 @@
       <c r="AB35" s="38"/>
       <c r="AC35" s="38"/>
     </row>
-    <row r="36" spans="3:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C36" s="47" t="s">
         <v>123</v>
       </c>
@@ -5585,7 +5585,7 @@
       <c r="AB36" s="37"/>
       <c r="AC36" s="37"/>
     </row>
-    <row r="37" spans="3:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C37" s="47" t="s">
         <v>124</v>
       </c>
@@ -5620,7 +5620,7 @@
       <c r="AB37" s="37"/>
       <c r="AC37" s="37"/>
     </row>
-    <row r="38" spans="3:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C38" s="47" t="s">
         <v>125</v>
       </c>
@@ -5655,7 +5655,7 @@
       <c r="AB38" s="38"/>
       <c r="AC38" s="38"/>
     </row>
-    <row r="39" spans="3:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C39" s="47" t="s">
         <v>126</v>
       </c>
@@ -5690,7 +5690,7 @@
       <c r="AB39" s="37"/>
       <c r="AC39" s="37"/>
     </row>
-    <row r="40" spans="3:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C40" s="47" t="s">
         <v>127</v>
       </c>
@@ -5725,7 +5725,7 @@
       <c r="AB40" s="37"/>
       <c r="AC40" s="37"/>
     </row>
-    <row r="41" spans="3:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:29" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C41" s="47" t="s">
         <v>128</v>
       </c>
@@ -5760,7 +5760,7 @@
       <c r="AB41" s="37"/>
       <c r="AC41" s="37"/>
     </row>
-    <row r="42" spans="3:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:29" ht="72" x14ac:dyDescent="0.3">
       <c r="C42" s="48" t="s">
         <v>129</v>
       </c>
@@ -5795,7 +5795,7 @@
       <c r="AB42" s="37"/>
       <c r="AC42" s="37"/>
     </row>
-    <row r="43" spans="3:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:29" ht="72" x14ac:dyDescent="0.3">
       <c r="C43" s="47" t="s">
         <v>131</v>
       </c>
@@ -5838,7 +5838,7 @@
       <c r="AB43" s="37"/>
       <c r="AC43" s="37"/>
     </row>
-    <row r="44" spans="3:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C44" s="47" t="s">
         <v>132</v>
       </c>
@@ -5881,7 +5881,7 @@
       <c r="AB44" s="37"/>
       <c r="AC44" s="37"/>
     </row>
-    <row r="45" spans="3:29" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:29" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="47" t="s">
         <v>133</v>
       </c>
@@ -5924,7 +5924,7 @@
       <c r="AB45" s="37"/>
       <c r="AC45" s="37"/>
     </row>
-    <row r="46" spans="3:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:29" x14ac:dyDescent="0.3">
       <c r="I46" s="41">
         <f t="shared" ref="I46:O46" si="0">SUM(I8:I45)</f>
         <v>1</v>
@@ -6025,21 +6025,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004C29EC1F39B9DD41BCCFBE989E63A9DC" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="fc06bebdbdf277271b3b7852d6872b8a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5b06a7d3-8a06-4fd7-88da-f0ff67c71e72" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0b5e6bf1bfa9b37807c2e0c964db186d" ns3:_="">
     <xsd:import namespace="5b06a7d3-8a06-4fd7-88da-f0ff67c71e72"/>
@@ -6223,24 +6208,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B985C0-369C-4698-BEEC-350B56DD384D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7BF84BE-6AFB-4495-8F40-8DFBF1912AB9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{387A6899-0EFD-41ED-99B2-369E509E51DA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6256,4 +6239,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7BF84BE-6AFB-4495-8F40-8DFBF1912AB9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B985C0-369C-4698-BEEC-350B56DD384D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>